--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22909,7 +22927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22953,6 +22971,71 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1976_77_0073 'TJ Slavoj Český Krumlov' ROZBITÝ prev CLUB_S1975_76_0103 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1976_77_0104 'TJ Tesla Liptovský Hrádok' ROZBITÝ prev CLUB_S1976_77_0579 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1976_77_0105 'TJ Jednota Kežmarok' ROZBITÝ prev CLUB_S1976_77_0580 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1976_77_0106 'TJ Slávia VŠP Nitra' prev→CLUB_S1975_76_0539 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0013</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1976_77_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1976_77_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -23924,7 +24007,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -56783,6 +56865,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0073</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0073 'TJ Slavoj Český Krumlov' ROZBITÝ prev CLUB_S1975_76_0103 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0104</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0104 'TJ Tesla Liptovský Hrádok' ROZBITÝ prev CLUB_S1976_77_0579 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0105</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0105 'TJ Jednota Kežmarok' ROZBITÝ prev CLUB_S1976_77_0580 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0106</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0106 'TJ Slávia VŠP Nitra' prev→CLUB_S1975_76_0539 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0013</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1976_77_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1976_77_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9706,6 +9706,11 @@
           <t>CLUB_S1975_76_0337</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr">
         <is>
           <t>TR_S1976_77_00308</t>
@@ -22927,7 +22932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22977,7 +22982,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1976_77_0073 'TJ Slavoj Český Krumlov' ROZBITÝ prev CLUB_S1975_76_0103 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22989,7 +22994,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1976_77_0104 'TJ Tesla Liptovský Hrádok' ROZBITÝ prev CLUB_S1976_77_0579 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23001,7 +23006,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1976_77_0105 'TJ Jednota Kežmarok' ROZBITÝ prev CLUB_S1976_77_0580 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23013,7 +23018,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1976_77_0106 'TJ Slávia VŠP Nitra' prev→CLUB_S1975_76_0539 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23023,17 +23028,564 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1976_77_0013</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1976_77_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1976_77_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1975_76_0539 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Petřvald' → 'Frýdek Místek' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0543 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0106 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24007,6 +24559,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -31622,12 +32175,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32225,12 +32778,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -32267,12 +32820,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -32398,12 +32951,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -32566,12 +33119,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -32692,12 +33245,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -33080,12 +33633,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -33515,12 +34068,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -33599,12 +34152,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -33809,12 +34362,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -34066,12 +34619,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34197,12 +34750,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -34239,12 +34792,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -34501,12 +35054,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -34543,12 +35096,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0103</t>
+          <t>CLUB_S1975_76_0184</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov. city OK. || Český Krumlov = Slavoj Český Krumlov (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Moravský Krumlov (Jihomoravsky). UNESCO mesto. city Český Krumlov.</t>
+          <t>Slavoj Český Krumlov. city OK. || Český Krumlov = Slavoj Český Krumlov (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Moravský Krumlov (Jihomoravsky). UNESCO mesto. city Český Krumlov. || TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -34753,12 +35306,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -34800,12 +35353,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity] || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -35057,12 +35610,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -35104,12 +35657,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -38519,12 +39072,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -40477,12 +41030,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Kněževes = JZD RŘ Kněževes (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Rakovník). 'RŘ' = pojmenovani druzstva. JZD = Jednotne zemedelske druzstvo. city Kněževes u Rakovníka.</t>
+          <t>Kněževes = JZD RŘ Kněževes (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Rakovník). 'RŘ' = pojmenovani druzstva. JZD = Jednotne zemedelske druzstvo. city Kněževes u Rakovníka. || TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>JZD RŘ Kněževes</t>
+          <t>Kněževes</t>
         </is>
       </c>
     </row>
@@ -40983,12 +41536,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -41722,12 +42275,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -41900,12 +42453,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -43626,12 +44179,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -46340,12 +46893,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -46481,12 +47034,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -46622,12 +47175,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -47314,12 +47867,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -48352,12 +48905,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -48488,12 +49041,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -51937,12 +52490,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -52518,12 +53071,12 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -53099,12 +53652,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -53823,12 +54376,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -54080,12 +54633,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -54122,12 +54675,12 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>A-tým Baník Petřvald Pionýr. Odstranění suffixu „A" (kolegova nedůslednost — A-tým je bez suffixu, D21). Oprava city: „Petřvald Pionýr A" → „Petřvald". Pionýr a Fučík = dva různé doly = dva samostatné kluby. || Petřvald = Banik Petřvald Julius Fučík (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina). Hornicke mesto. Patterns: Sokol -&gt; Banik -&gt; Petřvald Fučík. S-II = sezona II. liga. POZOR: NE Petřvald u Nového Jicina. city Petřvald.</t>
+          <t>A-tým Baník Petřvald Pionýr. Odstranění suffixu „A" (kolegova nedůslednost — A-tým je bez suffixu, D21). Oprava city: „Petřvald Pionýr A" → „Petřvald". Pionýr a Fučík = dva různé doly = dva samostatné kluby. || Petřvald = Banik Petřvald Julius Fučík (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina). Hornicke mesto. Patterns: Sokol -&gt; Banik -&gt; Petřvald Fučík. S-II = sezona II. liga. POZOR: NE Petřvald u Nového Jicina. city Petřvald. || TBD: city 'Petřvald' → 'Frýdek Místek' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Petřvald</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -54216,12 +54769,12 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek. || TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>VP Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -55828,12 +56381,12 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek. || TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>VP Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -55870,12 +56423,12 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>Nitra = TJ Slávia VŠP Nitra (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **VŠP** = Vysoká škola pedagogická (dnes Univerzita Konštantína Filozofa, UKF Nitra). city Nitra.</t>
+          <t>Nitra = TJ Slávia VŠP Nitra (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **VŠP** = Vysoká škola pedagogická (dnes Univerzita Konštantína Filozofa, UKF Nitra). city Nitra. || TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>Slávia VŠP Nitra</t>
+          <t>VŠP Nitra</t>
         </is>
       </c>
     </row>
@@ -55912,12 +56465,12 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom.</t>
+          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom. || TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>Družstevník Krizovany nad Dudváhom</t>
+          <t>Krizovany nad Dudváhom</t>
         </is>
       </c>
     </row>
@@ -56871,11 +57424,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -56920,21 +57473,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0073</t>
+          <t>CLUB_S1976_77_0005</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0073 'TJ Slavoj Český Krumlov' ROZBITÝ prev CLUB_S1975_76_0103 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -56942,21 +57493,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0104</t>
+          <t>CLUB_S1976_77_0019</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0104 'TJ Tesla Liptovský Hrádok' ROZBITÝ prev CLUB_S1976_77_0579 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -56964,21 +57513,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0105</t>
+          <t>CLUB_S1976_77_0020</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0105 'TJ Jednota Kežmarok' ROZBITÝ prev CLUB_S1976_77_0580 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -56986,21 +57533,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0106</t>
+          <t>CLUB_S1976_77_0023</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0106 'TJ Slávia VŠP Nitra' prev→CLUB_S1975_76_0539 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -57008,24 +57553,942 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1976_77_0013</t>
+          <t>CLUB_S1976_77_0027</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1976_77_0013 'Kvalifikace o 1. ČNHL' (L25, parent=NODE_S1976_77_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0030</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0039</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0049</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0051</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0056</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0062</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0065</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0066</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0072</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0073</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0078</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0079</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0079</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0085</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0086</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0106</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1975_76_0539 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0168</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0212</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0226</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0243</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0243</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0247</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0259</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0286</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0349</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0352</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0355</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0372</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0396</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0399</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0412</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0448</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0476</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0477</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0485</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0490</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0504</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0521</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0527</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0528</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Petřvald' → 'Frýdek Místek' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0530</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0566</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0569</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0570</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0576</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0543 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1976_77_0589</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0106 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -60521,7 +61984,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>CLUB_S1975_76_0103</t>
+          <t>CLUB_S1975_76_0184</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22932,7 +22932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22982,7 +22982,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22994,7 +22994,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23018,7 +23018,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23030,7 +23030,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23042,7 +23042,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23054,7 +23054,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23066,7 +23066,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23078,7 +23078,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23102,7 +23102,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23114,7 +23114,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23126,7 +23126,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23138,7 +23138,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23150,7 +23150,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1975_76_0539 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23162,7 +23162,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23186,7 +23186,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23198,7 +23198,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23210,7 +23210,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23222,7 +23222,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1975_76_0539 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -23234,7 +23234,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -23246,7 +23246,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -23270,7 +23270,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23282,7 +23282,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23294,7 +23294,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -23306,7 +23306,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23318,7 +23318,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23330,7 +23330,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23354,7 +23354,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23366,7 +23366,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -23378,7 +23378,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -23390,7 +23390,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -23402,7 +23402,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23414,7 +23414,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -23438,7 +23438,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0543 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23450,142 +23450,10 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0106 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Petřvald' → 'Frýdek Místek' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0543 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0106 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23602,7 +23470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23661,6 +23529,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23703,6 +23576,11 @@
           <t>12 týmů, jeden stůl. Mistr: Poldi SONP Kladno.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23750,6 +23628,11 @@
           <t>Série Opava – Trenčín 2:4. 1., 2. a 5. utkání v Opavě; případné 7. v Košicích; Trenčín hrál doma v Topoľčanech; prodloužení 3x5 min + nájezdy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23792,6 +23675,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK). Kvalifikace o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23834,6 +23722,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23876,6 +23769,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23918,6 +23816,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23960,6 +23863,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24002,6 +23910,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24044,6 +23957,11 @@
           <t>II.ČNHL: 3 skupiny po 8. Nově založená soutěž.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24086,6 +24004,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24128,6 +24051,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24170,6 +24098,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24217,6 +24150,11 @@
           <t>Tříčlenná tabulka Přerov – Jihlava "B" – VTJ Písek.</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24259,6 +24197,11 @@
           <t>Divize: 6 skupin CZ (A-F) + SVK západ/východ + kvalifikace.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24301,6 +24244,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0016</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24343,6 +24291,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0017</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24385,6 +24338,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0018</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24427,6 +24385,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0019</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24469,6 +24432,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0021</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24511,6 +24479,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24556,6 +24529,11 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>Finále BEZ Bratislava – Michalovce 3:1; jednotlivé výsledky viz SERIES.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0022</t>
         </is>
       </c>
     </row>
@@ -24690,6 +24668,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24816,6 +24799,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24858,6 +24846,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -24984,6 +24977,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0038</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -25283,6 +25281,11 @@
           <t>kvalifikace o II.třídu (přeborníci okresů)</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0039</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -25493,6 +25496,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25535,6 +25543,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25577,6 +25590,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25619,6 +25637,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25661,6 +25684,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -25708,6 +25736,11 @@
           <t>o postup do KP</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -25755,6 +25788,11 @@
           <t>Kvalifikace o KP II.třídy</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0050</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -25797,6 +25835,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0051</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -25839,6 +25882,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0052</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25881,6 +25929,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25923,6 +25976,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25965,6 +26023,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -26007,6 +26070,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0056</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26054,6 +26122,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26096,6 +26169,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0058</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -26138,6 +26216,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26222,6 +26305,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -26264,6 +26352,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0062</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -26306,6 +26399,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26348,6 +26446,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0065</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -26390,6 +26493,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0066</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -26516,6 +26624,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0069</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26642,6 +26755,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0070</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26684,6 +26802,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0071</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26726,6 +26849,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0072</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26768,6 +26896,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0073</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -26862,6 +26995,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0075</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26904,6 +27042,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0076</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26946,6 +27089,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0077</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26988,6 +27136,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0078</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -27030,6 +27183,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0079</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27072,6 +27230,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0080</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27371,6 +27534,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0086</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27413,6 +27581,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0087</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27581,6 +27754,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0091</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -27796,6 +27974,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0096</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -27838,6 +28021,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0097</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -27878,6 +28066,11 @@
       <c r="J101" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1975_76_0098</t>
         </is>
       </c>
     </row>
@@ -32175,12 +32368,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32820,12 +33013,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -32951,12 +33144,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -33245,12 +33438,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -34152,12 +34345,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -35657,12 +35850,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -42275,12 +42468,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -49041,12 +49234,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -52490,12 +52683,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -53652,12 +53845,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -54675,12 +54868,12 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>A-tým Baník Petřvald Pionýr. Odstranění suffixu „A" (kolegova nedůslednost — A-tým je bez suffixu, D21). Oprava city: „Petřvald Pionýr A" → „Petřvald". Pionýr a Fučík = dva různé doly = dva samostatné kluby. || Petřvald = Banik Petřvald Julius Fučík (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina). Hornicke mesto. Patterns: Sokol -&gt; Banik -&gt; Petřvald Fučík. S-II = sezona II. liga. POZOR: NE Petřvald u Nového Jicina. city Petřvald. || TBD: city 'Petřvald' → 'Frýdek Místek' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>A-tým Baník Petřvald Pionýr. Odstranění suffixu „A" (kolegova nedůslednost — A-tým je bez suffixu, D21). Oprava city: „Petřvald Pionýr A" → „Petřvald". Pionýr a Fučík = dva různé doly = dva samostatné kluby. || Petřvald = Banik Petřvald Julius Fučík (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina). Hornicke mesto. Patterns: Sokol -&gt; Banik -&gt; Petřvald Fučík. S-II = sezona II. liga. POZOR: NE Petřvald u Nového Jicina. city Petřvald.</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Frýdek Místek</t>
+          <t>Petřvald</t>
         </is>
       </c>
     </row>
@@ -57424,7 +57617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57478,12 +57671,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0005</t>
+          <t>CLUB_S1976_77_0019</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57498,12 +57691,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0019</t>
+          <t>CLUB_S1976_77_0027</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57518,12 +57711,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0020</t>
+          <t>CLUB_S1976_77_0039</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57538,12 +57731,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0023</t>
+          <t>CLUB_S1976_77_0049</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57558,12 +57751,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0027</t>
+          <t>CLUB_S1976_77_0056</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57578,12 +57771,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0030</t>
+          <t>CLUB_S1976_77_0062</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57598,12 +57791,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0039</t>
+          <t>CLUB_S1976_77_0065</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57618,12 +57811,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0049</t>
+          <t>CLUB_S1976_77_0066</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57638,12 +57831,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0051</t>
+          <t>CLUB_S1976_77_0072</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57658,12 +57851,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0056</t>
+          <t>CLUB_S1976_77_0073</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -57678,12 +57871,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0062</t>
+          <t>CLUB_S1976_77_0078</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57698,12 +57891,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0065</t>
+          <t>CLUB_S1976_77_0079</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57718,12 +57911,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0066</t>
+          <t>CLUB_S1976_77_0079</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57738,12 +57931,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0072</t>
+          <t>CLUB_S1976_77_0085</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57758,12 +57951,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0073</t>
+          <t>CLUB_S1976_77_0106</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1975_76_0184 'Slavoj Český Krumlov'; ověřit [fix_broken_prev_d42]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1975_76_0539 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57778,12 +57971,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0078</t>
+          <t>CLUB_S1976_77_0168</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57798,12 +57991,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0079</t>
+          <t>CLUB_S1976_77_0212</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0546 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57818,12 +58011,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0079</t>
+          <t>CLUB_S1976_77_0226</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57838,12 +58031,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0085</t>
+          <t>CLUB_S1976_77_0243</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57858,12 +58051,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0086</t>
+          <t>CLUB_S1976_77_0247</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57878,12 +58071,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0106</t>
+          <t>CLUB_S1976_77_0259</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1975_76_0539 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -57898,12 +58091,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0168</t>
+          <t>CLUB_S1976_77_0286</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57918,12 +58111,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0212</t>
+          <t>CLUB_S1976_77_0349</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'JZD RŘ Kněževes' → 'Kněževes' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57938,12 +58131,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0226</t>
+          <t>CLUB_S1976_77_0352</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57958,12 +58151,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0243</t>
+          <t>CLUB_S1976_77_0355</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57978,12 +58171,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0243</t>
+          <t>CLUB_S1976_77_0372</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57998,12 +58191,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0247</t>
+          <t>CLUB_S1976_77_0396</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58018,12 +58211,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0259</t>
+          <t>CLUB_S1976_77_0412</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -58038,12 +58231,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0286</t>
+          <t>CLUB_S1976_77_0448</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58058,12 +58251,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0349</t>
+          <t>CLUB_S1976_77_0476</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58078,12 +58271,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0352</t>
+          <t>CLUB_S1976_77_0485</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -58098,12 +58291,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0355</t>
+          <t>CLUB_S1976_77_0490</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58118,12 +58311,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0372</t>
+          <t>CLUB_S1976_77_0521</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58138,12 +58331,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0396</t>
+          <t>CLUB_S1976_77_0527</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58158,12 +58351,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0399</t>
+          <t>CLUB_S1976_77_0530</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58178,12 +58371,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0412</t>
+          <t>CLUB_S1976_77_0566</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58198,12 +58391,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0448</t>
+          <t>CLUB_S1976_77_0569</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58218,12 +58411,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0476</t>
+          <t>CLUB_S1976_77_0570</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58238,12 +58431,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0477</t>
+          <t>CLUB_S1976_77_0576</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0543 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -58258,237 +58451,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1976_77_0485</t>
+          <t>CLUB_S1976_77_0589</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0490</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0504</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0521</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0527</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0528</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Petřvald' → 'Frýdek Místek' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0530</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0566</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0569</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slávia VŠP Nitra' → 'VŠP Nitra' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0570</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0576</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0543 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1976_77_0589</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1975_76_0106 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M15" t="n">
         <v>12</v>

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -63464,7 +63464,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M38" t="n">
         <v>27</v>
@@ -63542,7 +63542,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M39" t="n">
         <v>26</v>
@@ -63708,7 +63708,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M41" t="n">
         <v>9</v>
@@ -63783,7 +63783,7 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
         <v>102</v>

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -23470,7 +23470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23534,6 +23534,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24537,7 +24547,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -23816,6 +23816,16 @@
           <t>NODE_S1976_77_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23830,6 +23840,14 @@
         <is>
           <t>NODE_S1975_76_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23863,6 +23881,8 @@
           <t>NODE_S1976_77_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23877,6 +23897,14 @@
         <is>
           <t>NODE_S1975_76_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -23910,6 +23938,8 @@
           <t>NODE_S1976_77_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23924,6 +23954,14 @@
         <is>
           <t>NODE_S1975_76_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -24526,6 +24564,8 @@
           <t>NODE_S1976_77_0014</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24546,7 +24586,16 @@
           <t>NODE_S1975_76_0022</t>
         </is>
       </c>
-    </row>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -24976,6 +25025,8 @@
           <t>NODE_S1976_77_0028</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24990,6 +25041,14 @@
         <is>
           <t>NODE_S1975_76_0038</t>
         </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -25233,6 +25292,8 @@
           <t>NODE_S1976_77_0028</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25242,6 +25303,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -26539,6 +26608,12 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0068</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26548,6 +26623,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -26581,6 +26664,12 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0068</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26590,6 +26679,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -26623,6 +26720,8 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26637,6 +26736,14 @@
         <is>
           <t>NODE_S1975_76_0069</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -26670,6 +26777,8 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26679,6 +26788,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -26712,6 +26829,8 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26721,6 +26840,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -27229,6 +27356,8 @@
           <t>NODE_S1976_77_0077</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27243,6 +27372,14 @@
         <is>
           <t>NODE_S1975_76_0080</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -27528,6 +27665,12 @@
           <t>REG_SVM</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NODE_S1976_77_0094</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27547,6 +27690,14 @@
         <is>
           <t>NODE_S1975_76_0086</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -27800,6 +27951,8 @@
           <t>NODE_S1976_77_0088</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27809,6 +27962,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="96">

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -720,6 +720,11 @@
           <t>Poldi SONP Kladno</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -23881,8 +23886,6 @@
           <t>NODE_S1976_77_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23938,8 +23941,6 @@
           <t>NODE_S1976_77_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24564,8 +24565,6 @@
           <t>NODE_S1976_77_0014</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24595,7 +24594,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -25025,8 +25023,6 @@
           <t>NODE_S1976_77_0028</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25292,8 +25288,6 @@
           <t>NODE_S1976_77_0028</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26613,7 +26607,6 @@
           <t>NODE_S1976_77_0068</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26669,7 +26662,6 @@
           <t>NODE_S1976_77_0068</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26720,8 +26712,6 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26777,8 +26767,6 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26829,8 +26817,6 @@
           <t>NODE_S1976_77_0064</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27356,8 +27342,6 @@
           <t>NODE_S1976_77_0077</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27670,7 +27654,6 @@
           <t>NODE_S1976_77_0094</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27951,8 +27934,6 @@
           <t>NODE_S1976_77_0088</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -57623,7 +57604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57773,6 +57754,18 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>Pro sezonu 1977/78 se ruší divize; nepostupující týmy padají do krajských přeborů.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Poldi SONP Kladno</t>
         </is>
       </c>
     </row>

--- a/data/S1976_77_FINAL.xlsx
+++ b/data/S1976_77_FINAL.xlsx
@@ -24594,6 +24594,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
